--- a/output/ATable-group-char.xlsx
+++ b/output/ATable-group-char.xlsx
@@ -466,59 +466,59 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>2682500</v>
+        <v>2992000</v>
       </c>
       <c r="D2">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E2">
-        <v>67.7</v>
+        <v>47.6</v>
       </c>
       <c r="F2">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G2">
-        <v>1973</v>
+        <v>1980</v>
       </c>
       <c r="H2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="I2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="J2">
-        <v>167.3</v>
+        <v>150.81</v>
       </c>
       <c r="K2">
-        <v>128.41</v>
+        <v>110.06</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="M2">
-        <v>76.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="N2">
-        <v>17745</v>
+        <v>15809</v>
       </c>
       <c r="O2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P2">
-        <v>27.4</v>
+        <v>23.8</v>
       </c>
       <c r="Q2">
-        <v>38.4</v>
+        <v>41.8</v>
       </c>
       <c r="R2">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="S2">
-        <v>11.9</v>
+        <v>15.1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Airport - Upscale - Large</t>
+          <t>Airport - Upscale - Medium</t>
         </is>
       </c>
     </row>
@@ -529,58 +529,58 @@
         </is>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>9929400</v>
+        <v>12988800</v>
       </c>
       <c r="D3">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E3">
         <v>100</v>
       </c>
       <c r="F3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G3">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="H3">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="I3">
-        <v>1091</v>
+        <v>991</v>
       </c>
       <c r="J3">
-        <v>167.72</v>
+        <v>162.93</v>
       </c>
       <c r="K3">
-        <v>131.59</v>
+        <v>124.45</v>
       </c>
       <c r="L3">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="M3">
-        <v>78.3</v>
+        <v>76.2</v>
       </c>
       <c r="N3">
-        <v>65169</v>
+        <v>71836</v>
       </c>
       <c r="O3">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="P3">
-        <v>21.8</v>
+        <v>20.4</v>
       </c>
       <c r="Q3">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="R3">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="S3">
-        <v>10.1</v>
+        <v>12.3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>7355600</v>
+        <v>8751600</v>
       </c>
       <c r="D4">
         <v>284</v>
@@ -616,22 +616,22 @@
         <v>2017</v>
       </c>
       <c r="I4">
-        <v>798</v>
+        <v>840</v>
       </c>
       <c r="J4">
-        <v>196.26</v>
+        <v>198.91</v>
       </c>
       <c r="K4">
-        <v>138.2</v>
+        <v>139.93</v>
       </c>
       <c r="L4">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M4">
-        <v>70.3</v>
+        <v>70.2</v>
       </c>
       <c r="N4">
-        <v>44667</v>
+        <v>44600</v>
       </c>
       <c r="O4">
         <v>96</v>
@@ -661,58 +661,58 @@
         </is>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>2409200</v>
+        <v>3106400</v>
       </c>
       <c r="D5">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5">
-        <v>50.3</v>
+        <v>45.2</v>
       </c>
       <c r="F5">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G5">
         <v>1958</v>
       </c>
       <c r="H5">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="I5">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J5">
-        <v>145.66</v>
+        <v>145.77</v>
       </c>
       <c r="K5">
-        <v>101.44</v>
+        <v>100.86</v>
       </c>
       <c r="L5">
         <v>2.1</v>
       </c>
       <c r="M5">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="N5">
-        <v>14046</v>
+        <v>14682</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="Q5">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
       <c r="R5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="S5">
-        <v>27.3</v>
+        <v>26.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -727,58 +727,58 @@
         </is>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>4758200</v>
+        <v>6142400</v>
       </c>
       <c r="D6">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E6">
-        <v>85.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G6">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="H6">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="I6">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="J6">
-        <v>178.86</v>
+        <v>178.75</v>
       </c>
       <c r="K6">
-        <v>126.92</v>
+        <v>125.84</v>
       </c>
       <c r="L6">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="M6">
-        <v>70.7</v>
+        <v>70.3</v>
       </c>
       <c r="N6">
-        <v>28708</v>
+        <v>30565</v>
       </c>
       <c r="O6">
         <v>92</v>
       </c>
       <c r="P6">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q6">
-        <v>41.6</v>
+        <v>40.3</v>
       </c>
       <c r="R6">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="S6">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -789,264 +789,264 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>4016600</v>
+        <v>8228000</v>
       </c>
       <c r="D7">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="E7">
-        <v>67.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="H7">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="I7">
-        <v>286</v>
+        <v>1622</v>
       </c>
       <c r="J7">
-        <v>311.31</v>
+        <v>266.36</v>
       </c>
       <c r="K7">
-        <v>222.51</v>
+        <v>213.38</v>
       </c>
       <c r="L7">
-        <v>6.8</v>
+        <v>12.7</v>
       </c>
       <c r="M7">
-        <v>71.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="N7">
-        <v>21968</v>
+        <v>47682</v>
       </c>
       <c r="O7">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="P7">
-        <v>51.5</v>
+        <v>58.3</v>
       </c>
       <c r="Q7">
-        <v>24.1</v>
+        <v>15.5</v>
       </c>
       <c r="R7">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="S7">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Hollywood/West LA - Luxury - Medium</t>
+          <t>Hollywood/West LA - Luxury - Large</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>9492400</v>
+        <v>4642000</v>
       </c>
       <c r="D8">
-        <v>312</v>
+        <v>117</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>67.3</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G8">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="H8">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="I8">
-        <v>739</v>
+        <v>317</v>
       </c>
       <c r="J8">
-        <v>254.41</v>
+        <v>316.27</v>
       </c>
       <c r="K8">
-        <v>198.99</v>
+        <v>226.31</v>
       </c>
       <c r="L8">
-        <v>15.8</v>
+        <v>7.1</v>
       </c>
       <c r="M8">
-        <v>78</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N8">
-        <v>62105</v>
+        <v>22317</v>
       </c>
       <c r="O8">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="P8">
-        <v>57.2</v>
+        <v>51.5</v>
       </c>
       <c r="Q8">
-        <v>17.2</v>
+        <v>24.1</v>
       </c>
       <c r="R8">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="S8">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Hollywood/West LA - Luxury - Mega</t>
+          <t>Hollywood/West LA - Luxury - Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T01</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>3021000</v>
+        <v>6767200</v>
       </c>
       <c r="D9">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="E9">
-        <v>55.8</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>1972</v>
+        <v>1992</v>
       </c>
       <c r="H9">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="I9">
-        <v>142</v>
+        <v>1347</v>
       </c>
       <c r="J9">
-        <v>209.24</v>
+        <v>225.51</v>
       </c>
       <c r="K9">
-        <v>157.54</v>
+        <v>166.39</v>
       </c>
       <c r="L9">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M9">
-        <v>75</v>
+        <v>73.5</v>
       </c>
       <c r="N9">
-        <v>18769</v>
+        <v>36052</v>
       </c>
       <c r="O9">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="P9">
-        <v>55.8</v>
+        <v>54.2</v>
       </c>
       <c r="Q9">
-        <v>18.1</v>
+        <v>21.3</v>
       </c>
       <c r="R9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="S9">
-        <v>13.9</v>
+        <v>11.7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Hollywood/West LA - Luxury - Small</t>
+          <t>Hollywood/West LA - Upscale - Large</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T01</t>
         </is>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>5844400</v>
+        <v>3476000</v>
       </c>
       <c r="D10">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="E10">
-        <v>88.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="F10">
+        <v>3.2</v>
+      </c>
+      <c r="G10">
+        <v>1972</v>
+      </c>
+      <c r="H10">
+        <v>2016</v>
+      </c>
+      <c r="I10">
+        <v>144</v>
+      </c>
+      <c r="J10">
+        <v>210.48</v>
+      </c>
+      <c r="K10">
+        <v>160.26</v>
+      </c>
+      <c r="L10">
         <v>4</v>
       </c>
-      <c r="G10">
-        <v>1992</v>
-      </c>
-      <c r="H10">
-        <v>2017</v>
-      </c>
-      <c r="I10">
-        <v>1338</v>
-      </c>
-      <c r="J10">
-        <v>224.17</v>
-      </c>
-      <c r="K10">
-        <v>163.96</v>
-      </c>
-      <c r="L10">
-        <v>8</v>
-      </c>
       <c r="M10">
-        <v>72.8</v>
+        <v>75.8</v>
       </c>
       <c r="N10">
-        <v>35659</v>
+        <v>19018</v>
       </c>
       <c r="O10">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="P10">
-        <v>54.2</v>
+        <v>55.9</v>
       </c>
       <c r="Q10">
-        <v>21.3</v>
+        <v>18</v>
       </c>
       <c r="R10">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>11.7</v>
+        <v>13.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Hollywood/West LA - Upscale - Large</t>
+          <t>Hollywood/West LA - Upscale - Small</t>
         </is>
       </c>
     </row>
@@ -1057,62 +1057,62 @@
         </is>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>10567200</v>
+        <v>12082400</v>
       </c>
       <c r="D11">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="E11">
-        <v>90.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="F11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G11">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="H11">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="I11">
-        <v>876</v>
+        <v>923</v>
       </c>
       <c r="J11">
-        <v>224.16</v>
+        <v>224</v>
       </c>
       <c r="K11">
-        <v>185.37</v>
+        <v>185.43</v>
       </c>
       <c r="L11">
         <v>16.3</v>
       </c>
       <c r="M11">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N11">
-        <v>72374</v>
+        <v>72422</v>
       </c>
       <c r="O11">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="P11">
-        <v>51</v>
+        <v>51.9</v>
       </c>
       <c r="Q11">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="R11">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="S11">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>North LA - Luxury - Large</t>
+          <t>North LA - Luxury - Mega</t>
         </is>
       </c>
     </row>
@@ -1123,58 +1123,58 @@
         </is>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>2564100</v>
+        <v>3489200</v>
       </c>
       <c r="D12">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E12">
-        <v>13.6</v>
+        <v>11.9</v>
       </c>
       <c r="F12">
         <v>2.9</v>
       </c>
       <c r="G12">
-        <v>1986</v>
+        <v>1991</v>
       </c>
       <c r="H12">
         <v>2019</v>
       </c>
       <c r="I12">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="J12">
-        <v>166.78</v>
+        <v>167.48</v>
       </c>
       <c r="K12">
-        <v>118.8</v>
+        <v>123.32</v>
       </c>
       <c r="L12">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M12">
-        <v>71.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="N12">
-        <v>15722</v>
+        <v>17474</v>
       </c>
       <c r="O12">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="P12">
-        <v>51.8</v>
+        <v>49.9</v>
       </c>
       <c r="Q12">
-        <v>26.5</v>
+        <v>25.1</v>
       </c>
       <c r="R12">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="S12">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1192,55 +1192,55 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>4021900</v>
+        <v>4760800</v>
       </c>
       <c r="D13">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>35.9</v>
+        <v>25</v>
       </c>
       <c r="F13">
         <v>3.2</v>
       </c>
       <c r="G13">
-        <v>1979</v>
+        <v>1988</v>
       </c>
       <c r="H13">
         <v>2021</v>
       </c>
       <c r="I13">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="J13">
-        <v>147.67</v>
+        <v>153.31</v>
       </c>
       <c r="K13">
-        <v>99.22</v>
+        <v>108.59</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="M13">
-        <v>67.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="N13">
-        <v>20034</v>
+        <v>23159</v>
       </c>
       <c r="O13">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P13">
-        <v>28.1</v>
+        <v>30.2</v>
       </c>
       <c r="Q13">
-        <v>47.1</v>
+        <v>47.9</v>
       </c>
       <c r="R13">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="S13">
-        <v>14.5</v>
+        <v>13.1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
